--- a/artfynd/A 62371-2023 artfynd.xlsx
+++ b/artfynd/A 62371-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62371-2023 artfynd.xlsx
+++ b/artfynd/A 62371-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108850973</v>
+        <v>108852418</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555111.8136843992</v>
+        <v>555145</v>
       </c>
       <c r="R2" t="n">
-        <v>6331154.801756131</v>
+        <v>6331148</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +752,9 @@
           <t>2022-01-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-01-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +765,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,47 +796,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108852418</v>
+        <v>108850973</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555145.0867675371</v>
+        <v>555112</v>
       </c>
       <c r="R3" t="n">
-        <v>6331148.187667813</v>
+        <v>6331155</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +869,9 @@
           <t>2022-01-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-01-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,21 +882,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 62371-2023 artfynd.xlsx
+++ b/artfynd/A 62371-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108852418</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,8 +905,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108850973</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>